--- a/artfynd/A 26362-2026 artfynd.xlsx
+++ b/artfynd/A 26362-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>76794839</v>
       </c>
       <c r="B2" t="n">
-        <v>98138</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99156</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,37 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>76794843</v>
+        <v>76794844</v>
       </c>
       <c r="B3" t="n">
-        <v>105102</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101897</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221725</v>
+        <v>220075</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,7 +819,7 @@
         <v>431272</v>
       </c>
       <c r="R3" t="n">
-        <v>6482391</v>
+        <v>6482377</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,12 +890,7 @@
         <v>76794828</v>
       </c>
       <c r="B4" t="n">
-        <v>105676</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>76794835</v>
+        <v>76794843</v>
       </c>
       <c r="B5" t="n">
-        <v>100188</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222771</v>
+        <v>221725</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,13 +1028,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>431222</v>
+        <v>431272</v>
       </c>
       <c r="R5" t="n">
-        <v>6482452</v>
+        <v>6482391</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,15 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103045516</v>
+        <v>103045518</v>
       </c>
       <c r="B6" t="n">
-        <v>103154</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222395</v>
+        <v>221725</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1159,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>431272</v>
+        <v>431263</v>
       </c>
       <c r="R6" t="n">
-        <v>6482377</v>
+        <v>6482381</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,15 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103045512</v>
+        <v>103045509</v>
       </c>
       <c r="B7" t="n">
-        <v>100188</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104253</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,16 +1216,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222771</v>
+        <v>222395</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1270,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>431273</v>
+        <v>431287</v>
       </c>
       <c r="R7" t="n">
-        <v>6482413</v>
+        <v>6482324</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,15 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103045509</v>
+        <v>103045516</v>
       </c>
       <c r="B8" t="n">
-        <v>103154</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104253</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>431287</v>
+        <v>431272</v>
       </c>
       <c r="R8" t="n">
-        <v>6482324</v>
+        <v>6482377</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,15 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103045518</v>
+        <v>76794835</v>
       </c>
       <c r="B9" t="n">
-        <v>105102</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,37 +1428,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221725</v>
+        <v>222771</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sjötorp NO, Vg</t>
+          <t>Sjötorp öster om, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>431263</v>
+        <v>431222</v>
       </c>
       <c r="R9" t="n">
-        <v>6482381</v>
+        <v>6482452</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1530,6 +1490,11 @@
           <t>2012-06-07</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Betesmark barrskog, lövskog, sumpskog, kärr och skogsvägar</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1538,24 +1503,125 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Skogsväg, Barrskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>103045512</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sjötorp NO, Vg</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>431273</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6482413</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2012-06-07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2012-06-07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Skogsväg, Barrskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Kurt-Anders Johansson</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr">
+      <c r="AY10" t="inlineStr">
         <is>
           <t>Billingens flora</t>
         </is>

--- a/artfynd/A 26362-2026 artfynd.xlsx
+++ b/artfynd/A 26362-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76794839</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76794844</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76794828</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76794843</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103045518</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103045509</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103045516</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76794835</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1626,8 +1671,24 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103045512</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>